--- a/resource/tabel pengujian.xlsx
+++ b/resource/tabel pengujian.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afit\OneDrive\Documents\Skripsi\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f4ed61fe0626ee0/Documents/Skripsi/resource/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E1D71A-6578-44BF-B1FE-A7F0844E0460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{21E1D71A-6578-44BF-B1FE-A7F0844E0460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE05502-8B68-485D-A7CF-7E7DDEEB0BD7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bisakah anda buatkan tabel peng" sheetId="1" r:id="rId1"/>
@@ -52,86 +52,248 @@
     <t>Test dengan larutan buffer</t>
   </si>
   <si>
-    <t>Pembacaan sesuai</t>
-  </si>
-  <si>
     <t>Sensor TDS</t>
   </si>
   <si>
     <t>Mencelupkan sensor ke air</t>
   </si>
   <si>
-    <t>Nilai TDS sesuai konsentrasi air.</t>
-  </si>
-  <si>
     <t>Sensor Suhu (DS18B20)</t>
   </si>
   <si>
     <t>Membandingkan suhu air dengan sensor</t>
   </si>
   <si>
-    <t>Selisih suhu sedikit</t>
-  </si>
-  <si>
     <t>Sensor Kekeruhan</t>
   </si>
   <si>
     <t>Menguji pada air jernih dan air keruh.</t>
   </si>
   <si>
-    <t>Nilai NTU sesuai</t>
-  </si>
-  <si>
     <t>Modul GPS</t>
   </si>
   <si>
     <t>Menyalakan alat di area terbuka.</t>
   </si>
   <si>
-    <t>Titik koordinat valid</t>
-  </si>
-  <si>
     <t>LCD Display</t>
   </si>
   <si>
     <t>Mengamati tampilan layar</t>
   </si>
   <si>
-    <t>Menampilkan data dengan jelas</t>
-  </si>
-  <si>
     <t>Konektivitas Wi-Fi</t>
   </si>
   <si>
     <t>Memantau status koneksi</t>
   </si>
   <si>
-    <t>Mendapatkan IP address</t>
-  </si>
-  <si>
     <t>Penyimpanan Lokal (SD Card)</t>
   </si>
   <si>
     <t>Memutus koneksi internet</t>
   </si>
   <si>
-    <t>Data tersimpan di kartu SD saat offline.</t>
-  </si>
-  <si>
     <t>Cloud (Firebase)</t>
   </si>
   <si>
     <t>Mengamati dashboard saat online</t>
   </si>
   <si>
-    <t>Data sensor masuk ke database</t>
+    <t>Terjadi perubahan pembacaan tegangan analog/ADC pada layar.</t>
+  </si>
+  <si>
+    <t>Terjadi pembacaan nilai raw TDS yang stabil.</t>
+  </si>
+  <si>
+    <t>Sistem menampilkan angka suhu aktual yang logis.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Terdapat fluktuasi pembacaan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>raw</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tegangan (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>turbidity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mendapatkan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> satelit dan titik koordinat tervalidasi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Menampilkan seluruh data parameter dengan jelas tanpa glitch.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Modul berhasil terhubung dan mendapatkan </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IP Address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Berhasil membuat </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> log .csv dan menyimpan data saat </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>offline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Titik data masuk ke struktur </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>database</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> secara </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>real-time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -144,8 +306,15 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +325,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,16 +344,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -186,15 +361,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,7 +597,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="D13:H23"/>
+  <dimension ref="C9:J29"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.109375" customWidth="1"/>
@@ -423,172 +607,305 @@
     <col min="7" max="7" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D13" s="1" t="s">
+    <row r="9" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+      <c r="D13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D14" s="2">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C14" s="1"/>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="2">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C15" s="1"/>
+      <c r="D15" s="3">
         <v>2</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C16" s="1"/>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C17" s="1"/>
+      <c r="D17" s="3">
+        <v>4</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C18" s="1"/>
+      <c r="D18" s="3">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C19" s="1"/>
+      <c r="D19" s="3">
+        <v>6</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="2">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
+      <c r="D20" s="3">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="2">
-        <v>6</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="G20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C21" s="1"/>
+      <c r="D21" s="3">
+        <v>8</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C22" s="1"/>
+      <c r="D22" s="3">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D20" s="2">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="F22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C23" s="1"/>
+      <c r="D23" s="3">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D21" s="2">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D22" s="2">
-        <v>9</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D23" s="2">
-        <v>10</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="6" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="3"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
